--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Demo.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{8936FD5D-6A82-472B-9B48-8132D385069F}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8936FD5D-6A82-472B-9B48-8132D385069F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="ManualEntry_CANAmount" r:id="rId1" sheetId="1"/>
-    <sheet name="ManualEntry_CANAmount_Error" r:id="rId2" sheetId="2"/>
+    <sheet name="ManualEntry_CANAmount" sheetId="1" r:id="rId1"/>
+    <sheet name="ManualEntry_CANAmount_Error" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="70">
   <si>
     <t>Result</t>
   </si>
@@ -204,21 +204,6 @@
     <t>UDF3</t>
   </si>
   <si>
-    <t>Wed Mar 25 18:37:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:38:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:38:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:39:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:39:58 IST 2026</t>
-  </si>
-  <si>
     <t>CANUsed</t>
   </si>
   <si>
@@ -229,162 +214,6 @@
   </si>
   <si>
     <t>N</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 17:43:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 17:44:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 17:45:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 17:46:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 17:47:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 17:48:32 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 17:57:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 17:59:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 18:00:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 18:01:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 18:01:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 04 18:02:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:07:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:08:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:09:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:10:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:11:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:11:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:12:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:13:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:14:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:15:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 18 02:16:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:54:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:55:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:56:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:57:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:57:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:58:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 13:59:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 14:00:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 14:01:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 14:02:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 14:03:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 14:03:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 14:04:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 14:05:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 14:06:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jun 29 14:06:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:37:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:38:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:39:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:39:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:40:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:41:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:42:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:43:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:44:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:45:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 15:46:13 IST 2026</t>
   </si>
   <si>
     <t>Thu Jul 09 18:59:07 IST 2026</t>
@@ -424,7 +253,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -532,69 +360,69 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="4" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="5" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="5" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="2" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="3" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle builtinId="8" name="Hyperlink" xfId="1"/>
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -611,10 +439,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -649,7 +477,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -701,7 +529,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -812,21 +640,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -843,7 +671,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -915,41 +743,41 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
   <dimension ref="A1:AD7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="6.7265625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="16.6328125" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="4" width="25.0" collapsed="true"/>
-    <col min="4" max="4" style="1" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="15.0" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="10.36328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="13.54296875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="6" width="12.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
-    <col min="10" max="11" customWidth="true" style="6" width="10.36328125" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="6" width="16.0" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="6" width="9.08984375" collapsed="true"/>
-    <col min="16" max="17" customWidth="true" style="6" width="14.453125" collapsed="true"/>
-    <col min="18" max="18" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
-    <col min="20" max="20" customWidth="true" style="6" width="12.0" collapsed="true"/>
-    <col min="21" max="21" customWidth="true" style="6" width="11.26953125" collapsed="true"/>
-    <col min="22" max="30" style="6" width="8.7265625" collapsed="true"/>
-    <col min="31" max="16384" style="1" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.7265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="16.6328125" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="25" style="4" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="1" collapsed="1"/>
+    <col min="5" max="5" width="15" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="10.36328125" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.54296875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="11" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="17.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="16" style="6" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="9.08984375" style="6" customWidth="1" collapsed="1"/>
+    <col min="16" max="17" width="14.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
+    <col min="20" max="20" width="12" style="6" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="11.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="22" max="30" width="8.7265625" style="6" collapsed="1"/>
+    <col min="31" max="16384" width="8.7265625" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -966,10 +794,10 @@
         <v>14</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>5</v>
@@ -993,7 +821,7 @@
         <v>17</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>7</v>
@@ -1041,12 +869,12 @@
         <v>24</v>
       </c>
     </row>
-    <row ht="37.5" r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="1">
+    <row r="2" spans="1:30" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B2" t="s" s="1">
-        <v>116</v>
+      <c r="B2" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>28</v>
@@ -1061,7 +889,7 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H2" s="6">
         <v>44489405</v>
@@ -1079,12 +907,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row ht="37.5" r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="1">
+    <row r="3" spans="1:30" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B3" t="s" s="1">
-        <v>117</v>
+      <c r="B3" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>33</v>
@@ -1096,7 +924,7 @@
         <v>49</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>4</v>
@@ -1117,12 +945,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row ht="62.5" r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="1">
+    <row r="4" spans="1:30" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B4" t="s" s="1">
-        <v>118</v>
+      <c r="B4" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>44</v>
@@ -1137,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H4" s="6">
         <v>44489405</v>
@@ -1158,12 +986,12 @@
         <v>22201</v>
       </c>
     </row>
-    <row ht="62.5" r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="1">
+    <row r="5" spans="1:30" ht="62.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B5" t="s" s="1">
-        <v>119</v>
+      <c r="B5" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>45</v>
@@ -1175,7 +1003,7 @@
         <v>49</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>4</v>
@@ -1199,12 +1027,12 @@
         <v>22201</v>
       </c>
     </row>
-    <row ht="37.5" r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="1">
+    <row r="6" spans="1:30" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B6" t="s" s="1">
-        <v>120</v>
+      <c r="B6" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>50</v>
@@ -1219,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H6" s="6">
         <v>44489405</v>
@@ -1264,12 +1092,12 @@
         <v>43</v>
       </c>
     </row>
-    <row ht="37.5" r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" t="s" s="1">
+    <row r="7" spans="1:30" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B7" t="s" s="1">
-        <v>121</v>
+      <c r="B7" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>51</v>
@@ -1281,7 +1109,7 @@
         <v>49</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>4</v>
@@ -1332,53 +1160,53 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="L3" xr:uid="{FE47C787-DE99-4492-A8B2-4EBE54ABB261}"/>
-    <hyperlink r:id="rId2" ref="L2" xr:uid="{D2C11198-27F8-408D-8A6B-64C9B9DF0F92}"/>
-    <hyperlink r:id="rId3" ref="L5" xr:uid="{6A159962-5D60-427C-9730-B7B753DCF218}"/>
-    <hyperlink r:id="rId4" ref="L4" xr:uid="{064B7228-C8DF-4F7F-9129-CEED06BA7374}"/>
-    <hyperlink r:id="rId5" ref="L6" xr:uid="{78C57E38-062F-4D27-A020-BB6599F0796C}"/>
-    <hyperlink r:id="rId6" ref="L7" xr:uid="{D354FF75-6436-4976-9A70-805C8AB59413}"/>
+    <hyperlink ref="L3" r:id="rId1" xr:uid="{FE47C787-DE99-4492-A8B2-4EBE54ABB261}"/>
+    <hyperlink ref="L2" r:id="rId2" xr:uid="{D2C11198-27F8-408D-8A6B-64C9B9DF0F92}"/>
+    <hyperlink ref="L5" r:id="rId3" xr:uid="{6A159962-5D60-427C-9730-B7B753DCF218}"/>
+    <hyperlink ref="L4" r:id="rId4" xr:uid="{064B7228-C8DF-4F7F-9129-CEED06BA7374}"/>
+    <hyperlink ref="L6" r:id="rId5" xr:uid="{78C57E38-062F-4D27-A020-BB6599F0796C}"/>
+    <hyperlink ref="L7" r:id="rId6" xr:uid="{D354FF75-6436-4976-9A70-805C8AB59413}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
   <dimension ref="A1:AE6"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="6" width="15.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="8" width="36.0" collapsed="true"/>
-    <col min="4" max="4" style="6" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="10.81640625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="6" width="9.36328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="6" width="11.36328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="10.7265625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="6" width="16.453125" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="6" width="12.0" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="6" width="16.0" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="6" width="12.0" collapsed="true"/>
-    <col min="16" max="16" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
-    <col min="17" max="17" customWidth="true" style="6" width="13.453125" collapsed="true"/>
-    <col min="18" max="19" style="6" width="8.7265625" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
-    <col min="21" max="21" customWidth="true" style="6" width="7.0" collapsed="true"/>
-    <col min="22" max="22" customWidth="true" style="6" width="7.36328125" collapsed="true"/>
-    <col min="23" max="24" style="6" width="8.7265625" collapsed="true"/>
-    <col min="25" max="25" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="26" max="26" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
-    <col min="27" max="27" customWidth="true" style="6" width="6.0" collapsed="true"/>
-    <col min="28" max="28" customWidth="true" style="6" width="5.90625" collapsed="true"/>
-    <col min="29" max="29" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="30" max="30" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
-    <col min="31" max="31" customWidth="true" style="8" width="47.08984375" collapsed="true"/>
-    <col min="32" max="32" customWidth="true" style="6" width="24.81640625" collapsed="true"/>
-    <col min="33" max="16384" style="6" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="15.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="36" style="8" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="6" collapsed="1"/>
+    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="10.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="9.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="11.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="10.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="10.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="16.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="12" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="16" style="6" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="12" style="6" customWidth="1" collapsed="1"/>
+    <col min="16" max="16" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="13.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="18" max="19" width="8.7265625" style="6" collapsed="1"/>
+    <col min="20" max="20" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="7" style="6" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="7.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="23" max="24" width="8.7265625" style="6" collapsed="1"/>
+    <col min="25" max="25" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="6" style="6" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="5.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="30" max="30" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="31" max="31" width="47.08984375" style="8" customWidth="1" collapsed="1"/>
+    <col min="32" max="32" width="24.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="33" max="16384" width="8.7265625" style="6" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
@@ -1398,10 +1226,10 @@
         <v>14</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>5</v>
@@ -1425,7 +1253,7 @@
         <v>17</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>7</v>
@@ -1476,12 +1304,12 @@
         <v>26</v>
       </c>
     </row>
-    <row ht="37.5" r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="6">
+    <row r="2" spans="1:31" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" t="s" s="6">
-        <v>122</v>
+      <c r="B2" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>27</v>
@@ -1520,12 +1348,12 @@
         <v>29</v>
       </c>
     </row>
-    <row ht="37.5" r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" t="s" s="6">
+    <row r="3" spans="1:31" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B3" t="s" s="6">
-        <v>123</v>
+      <c r="B3" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>30</v>
@@ -1591,12 +1419,12 @@
         <v>29</v>
       </c>
     </row>
-    <row ht="37.5" r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" t="s" s="6">
+    <row r="4" spans="1:31" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B4" t="s" s="6">
-        <v>124</v>
+      <c r="B4" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>31</v>
@@ -1632,12 +1460,12 @@
         <v>29</v>
       </c>
     </row>
-    <row customHeight="1" ht="42" r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" t="s" s="6">
+    <row r="5" spans="1:31" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B5" t="s" s="6">
-        <v>125</v>
+      <c r="B5" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>32</v>
@@ -1674,12 +1502,12 @@
         <v>29</v>
       </c>
     </row>
-    <row ht="50" r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" t="s" s="6">
+    <row r="6" spans="1:31" ht="50" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B6" t="s" s="6">
-        <v>126</v>
+      <c r="B6" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>46</v>
@@ -1726,12 +1554,12 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="L2" xr:uid="{116CABED-82C4-49A6-B1D3-FB007D34A91E}"/>
-    <hyperlink r:id="rId2" ref="L3" xr:uid="{8C433AE8-EA1A-4C8E-A7C0-0BB281ABB9A1}"/>
-    <hyperlink r:id="rId3" ref="L4" xr:uid="{A312AB03-1536-49D3-9B02-6827CCAB91D2}"/>
-    <hyperlink r:id="rId4" ref="L6" xr:uid="{FDC2FBF7-47EE-439C-A052-EF8B1027F8CA}"/>
+    <hyperlink ref="L2" r:id="rId1" xr:uid="{116CABED-82C4-49A6-B1D3-FB007D34A91E}"/>
+    <hyperlink ref="L3" r:id="rId2" xr:uid="{8C433AE8-EA1A-4C8E-A7C0-0BB281ABB9A1}"/>
+    <hyperlink ref="L4" r:id="rId3" xr:uid="{A312AB03-1536-49D3-9B02-6827CCAB91D2}"/>
+    <hyperlink ref="L6" r:id="rId4" xr:uid="{FDC2FBF7-47EE-439C-A052-EF8B1027F8CA}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>